--- a/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8F6D92-8A02-4757-873D-A53FB2F14B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD2718A-4524-40C0-BDFA-699878C85453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="300" windowWidth="37170" windowHeight="19920" firstSheet="1" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -481,6 +481,11 @@
     <definedName name="Table_N_j_Consumer_1">'4.7.1.1-2 Manure Methane'!$D$91:$E$99</definedName>
     <definedName name="Table_NE_j">'4.7.1.3-4 Soil Direct N2O'!$D$31:$E$39</definedName>
     <definedName name="Table_VS_j">'4.7.1.1-2 Manure Methane'!$D$22:$E$30</definedName>
+    <definedName name="VEERG_4_7_1_1__1_TotalAnnualMethaneProductionFromManureManagementOtherLivestock_Result_Method1">'4.7.1.1-2 Manure Methane'!$E$113</definedName>
+    <definedName name="VEERG_4_7_1_1__1_TotalAnnualMethaneProductionFromManureManagementOtherLivestock_Result_Method2">'4.7.1.1-2 Manure Methane'!$O$113</definedName>
+    <definedName name="VEERG_4_7_1_3__1_DirectNitrousOxideEmissionsFromSoil_Result_Method1">'4.7.1.3-4 Soil Direct N2O'!$E$70</definedName>
+    <definedName name="VEERG_4_7_1_5__1_AtmosphericDepositionEmissionsFromPasture_Result_Method1">'4.7.1.5-6 Soil Atmos Deposition'!$E$81</definedName>
+    <definedName name="VEERG_4_7_1_7__1_LeachingAndRunoffEmissionsFromPasture_Result_Method1">'4.7.1.7-8 Soil Leaching Runoff'!$E$72</definedName>
     <definedName name="X_Cell_OtherLivestock_Buffalo_CalculatedMMSAnaerobicLagoon">'Input - Other Livestock'!$E$14</definedName>
     <definedName name="X_Cell_OtherLivestock_Buffalo_CalculatedMMSPastureRangeAndPaddock">'Input - Other Livestock'!$E$13</definedName>
     <definedName name="X_Cell_OtherLivestock_Buffalo_FencedWater">'Input - Other Livestock'!$E$10</definedName>
@@ -9582,7 +9587,7 @@
     <tableColumn id="1" xr3:uid="{C1BE61FE-4062-42B2-A2C3-5D1021EC5783}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{068A837D-7F3F-459D-A755-48E9682BAEAC}" name="Mj" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{068A837D-7F3F-459D-A755-48E9682BAEAC}" name="Mj" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9720,49 +9725,49 @@
     <tableColumn id="1" xr3:uid="{B2A17227-E969-4ADF-87E0-0371E8053C47}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0ED77410-E0A5-414E-99F1-DAA2888A94C3}" name="MAT" totalsRowDxfId="59" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0ED77410-E0A5-414E-99F1-DAA2888A94C3}" name="MAT" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7DE9F1C0-B774-48E6-8BB2-55E1C69B4C97}" name="MAP" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{7DE9F1C0-B774-48E6-8BB2-55E1C69B4C97}" name="MAP" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{79A6ECD6-40A4-4C83-B239-A27BC9EB0FDF}" name="Frost days per year" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{79A6ECD6-40A4-4C83-B239-A27BC9EB0FDF}" name="Frost days per year" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E44E6E93-6421-4389-9FCA-AF62B86D4D30}" name="Elevation" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E44E6E93-6421-4389-9FCA-AF62B86D4D30}" name="Elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2C8C1CF4-E340-4927-88DB-99EF86BB2612}" name="MAP:PET" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{2C8C1CF4-E340-4927-88DB-99EF86BB2612}" name="MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{1793FB6E-13F5-413B-9DDD-06182C738039}" name="Min temp" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{1793FB6E-13F5-413B-9DDD-06182C738039}" name="Min temp" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{70E0410D-47ED-47C7-89DB-CD43B8842923}" name="Max temp" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{70E0410D-47ED-47C7-89DB-CD43B8842923}" name="Max temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{670D5E29-790E-4240-A01E-1874ECF8A90D}" name="Min rainfall" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{670D5E29-790E-4240-A01E-1874ECF8A90D}" name="Min rainfall" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{94DD7AD8-73BB-4413-B275-E214837BB9A6}" name="Max rainfall" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{94DD7AD8-73BB-4413-B275-E214837BB9A6}" name="Max rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{468662A2-51BA-45A2-B4FA-0832B9C7A6BC}" name="Min frost days" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{468662A2-51BA-45A2-B4FA-0832B9C7A6BC}" name="Min frost days" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5C1C2169-AB74-4179-8C42-976FC003BEC6}" name="Max frost days" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{5C1C2169-AB74-4179-8C42-976FC003BEC6}" name="Max frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{42F6E499-84FA-463B-A79B-B19D09EA6147}" name="Min elevation" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{42F6E499-84FA-463B-A79B-B19D09EA6147}" name="Min elevation" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{6DE0B931-AB3B-4CC8-9D83-2DCCD0AEB2B2}" name="Max elevation" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{6DE0B931-AB3B-4CC8-9D83-2DCCD0AEB2B2}" name="Max elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C9FE892C-0E22-4FEF-B299-E370BD512A09}" name="Min MAP:PET" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{C9FE892C-0E22-4FEF-B299-E370BD512A09}" name="Min MAP:PET" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C7AFCB2D-51AB-4BA5-A24E-587A5EB6874E}" name="Max MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{C7AFCB2D-51AB-4BA5-A24E-587A5EB6874E}" name="Max MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9780,7 +9785,7 @@
     <tableColumn id="1" xr3:uid="{735271A4-264D-4C8A-9489-BED422FA01C2}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6969A27-E25C-4216-9C8A-B15164CD6269}" name="Wet or Dry Zone" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B6969A27-E25C-4216-9C8A-B15164CD6269}" name="Wet or Dry Zone" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9859,16 +9864,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="21" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="58" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{224F01F5-9F04-424C-9B4C-94B1D666F42B}" name="Other livestock type" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{224F01F5-9F04-424C-9B4C-94B1D666F42B}" name="Other livestock type" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D62AC0D1-1095-4EC7-994A-E2C80051C1F2}" name="VSj" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D62AC0D1-1095-4EC7-994A-E2C80051C1F2}" name="VSj" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9904,7 +9909,7 @@
     <tableColumn id="1" xr3:uid="{3AB08733-E779-478E-B0E9-97B28C19C11B}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FE2EE01B-9E26-449A-815F-9876C8AEAD91}" name="FracWET" dataDxfId="43">
+    <tableColumn id="2" xr3:uid="{FE2EE01B-9E26-449A-815F-9876C8AEAD91}" name="FracWET" dataDxfId="20">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9952,7 +9957,7 @@
     <tableColumn id="1" xr3:uid="{6D4F1866-1104-48B8-9926-1AAD31F861D3}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E364334A-82AD-4C7C-B3B5-1F033430EA56}" name="FracWET" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E364334A-82AD-4C7C-B3B5-1F033430EA56}" name="FracWET" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9970,7 +9975,7 @@
     <tableColumn id="1" xr3:uid="{C7B99F02-AB40-4134-B67A-E019FD248BDD}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{068DCC5A-5CC1-43F1-A318-492A13374BA7}" name="EFPRP" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{068DCC5A-5CC1-43F1-A318-492A13374BA7}" name="EFPRP" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9988,7 +9993,7 @@
     <tableColumn id="1" xr3:uid="{0783121C-7BDB-452D-A5E4-8D0E3554F3DB}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BCE36B2D-0C6D-4FD7-868A-2E2A9DD6DE11}" name="Season" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BCE36B2D-0C6D-4FD7-868A-2E2A9DD6DE11}" name="Season" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10020,49 +10025,49 @@
     <tableColumn id="1" xr3:uid="{8F0533C0-C167-4120-A701-D6DDDE9B53BB}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{37381098-C00C-4159-BB35-616E17C7AC15}" name="MAT (ºC)" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{37381098-C00C-4159-BB35-616E17C7AC15}" name="MAT (ºC)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5E3D06F8-EFDC-4B0A-AEC1-B70E72069C48}" name="Anaerobic lagoon" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5E3D06F8-EFDC-4B0A-AEC1-B70E72069C48}" name="Anaerobic lagoon" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9BF96835-D68B-410A-9C08-3B8AA3C17F89}" name="Digester / covered lagoons" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{9BF96835-D68B-410A-9C08-3B8AA3C17F89}" name="Digester / covered lagoons" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{ACF34BBC-3B58-4752-BDF3-C74E8B77FA6E}" name="Liquid systems" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{ACF34BBC-3B58-4752-BDF3-C74E8B77FA6E}" name="Liquid systems" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6FF6510A-FBC8-472D-87CF-28ADA0992391}" name="Daily spread" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{6FF6510A-FBC8-472D-87CF-28ADA0992391}" name="Daily spread" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3061CE58-E21B-4BEE-A59C-B5481B9563B8}" name="Composting (passive windrow)" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3061CE58-E21B-4BEE-A59C-B5481B9563B8}" name="Composting (passive windrow)" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{53E1449F-D0C6-4523-926C-92C357B3DD23}" name="Solid storage" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{53E1449F-D0C6-4523-926C-92C357B3DD23}" name="Solid storage" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{CBA287A5-0A1F-4EA9-9B37-C44DEC7567F2}" name="Pit storage" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{CBA287A5-0A1F-4EA9-9B37-C44DEC7567F2}" name="Pit storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AB8925C3-3A08-49B2-894C-BBFF7566F65D}" name="Deep litter" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{AB8925C3-3A08-49B2-894C-BBFF7566F65D}" name="Deep litter" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A5FE956A-CEB4-4903-A7AB-BBD5A71D7DA4}" name="Poultry manure with bedding" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{A5FE956A-CEB4-4903-A7AB-BBD5A71D7DA4}" name="Poultry manure with bedding" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A4F94ACC-10AB-4ABF-8C58-809A7381A8C0}" name="Poultry manure without bedding" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{A4F94ACC-10AB-4ABF-8C58-809A7381A8C0}" name="Poultry manure without bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{34EA0671-7442-43E2-ACA2-B4E7A99F00F2}" name="Direct processing" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{34EA0671-7442-43E2-ACA2-B4E7A99F00F2}" name="Direct processing" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F34704C3-0E95-45DD-AEEF-A79860DFA749}" name="Direct application" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{F34704C3-0E95-45DD-AEEF-A79860DFA749}" name="Direct application" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1A1607BD-814A-47FD-BF2B-17DF78EB4EEA}" name="Pasture range and paddock" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{1A1607BD-814A-47FD-BF2B-17DF78EB4EEA}" name="Pasture range and paddock" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{CDB602E1-649F-4B2B-8DAB-AAB461C9300B}" name="MAT raw" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{CDB602E1-649F-4B2B-8DAB-AAB461C9300B}" name="MAT raw" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10080,7 +10085,7 @@
     <tableColumn id="1" xr3:uid="{B77FA3D5-4E92-4E9F-9BEF-61B57C75CFCA}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ACD39327-4BD7-4D24-9036-E6912D7DFE98}" name="EFNi &amp; EFN2Oi" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{ACD39327-4BD7-4D24-9036-E6912D7DFE98}" name="EFNi &amp; EFN2Oi" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10096,7 +10101,7 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{B26FA8F1-6413-4D07-8E37-4191A8C81055}" name="Description" dataDxfId="23" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{B26FA8F1-6413-4D07-8E37-4191A8C81055}" name="Description" dataDxfId="0" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{E663688C-4BCA-4A83-B673-1238D7A5B9A4}" name="ID"/>
     <tableColumn id="3" xr3:uid="{0255E234-D646-413F-B7AB-DACD6D932AC0}" name="Score"/>
   </tableColumns>
@@ -10121,16 +10126,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="18" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="55" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{99F8CB88-8A74-44CD-B1D3-22D4849941C6}" name="Other livestock type" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{99F8CB88-8A74-44CD-B1D3-22D4849941C6}" name="Other livestock type" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CD5FC568-A825-4281-84C4-C2307E67DC49}" name="NEj" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CD5FC568-A825-4281-84C4-C2307E67DC49}" name="NEj" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10171,20 +10176,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="15" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="52" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{816644D3-41EE-45F6-A3CE-CACB3EB69547}" name="Other livestock type" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{816644D3-41EE-45F6-A3CE-CACB3EB69547}" name="Other livestock type" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53512804-9E08-42E2-B55E-1C89A4C09FEE}" name="Wco" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53512804-9E08-42E2-B55E-1C89A4C09FEE}" name="Wco" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0BB31A55-829C-489B-82D5-5810EC5F02C8}" name="Wco2" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0BB31A55-829C-489B-82D5-5810EC5F02C8}" name="Wco2" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10193,20 +10198,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="48" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A6CB9AC6-F6CE-49B7-A982-F82076716CA3}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{A6CB9AC6-F6CE-49B7-A982-F82076716CA3}" name="Other livestock type" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8AFBE1CB-9936-4A35-A761-4DCB7B6BA889}" name="Pasture range and paddock" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8AFBE1CB-9936-4A35-A761-4DCB7B6BA889}" name="Pasture range and paddock" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{95A534B1-6D18-468E-ACD4-CB91F74DE859}" name="Uncovered anaerobic lagoon" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{95A534B1-6D18-468E-ACD4-CB91F74DE859}" name="Uncovered anaerobic lagoon" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10215,20 +10220,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="44" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8D99AA70-8F55-4D11-BC0B-A089B4E9846C}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{8D99AA70-8F55-4D11-BC0B-A089B4E9846C}" name="Other livestock type" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8669BCCE-EDA0-482F-B818-E7495ADAD605}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8669BCCE-EDA0-482F-B818-E7495ADAD605}" name="Pasture range and paddock" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F18CF34C-B873-434B-8D03-00492CEC1FC6}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F18CF34C-B873-434B-8D03-00492CEC1FC6}" name="Uncovered anaerobic lagoon" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10237,20 +10242,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}" name="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" displayName="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" ref="D102:F110" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}" name="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" displayName="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" ref="D102:F110" totalsRowShown="0" dataDxfId="40" dataCellStyle="Content normal">
   <autoFilter ref="D102:F110" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5720D920-9C04-4E20-8D42-759F7E36C7D8}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{5720D920-9C04-4E20-8D42-759F7E36C7D8}" name="Other livestock type" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E9A32AB0-4663-4816-913A-79DAAFF08391}" name="BO" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E9A32AB0-4663-4816-913A-79DAAFF08391}" name="BO" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{35962C17-3057-4CB9-8C5C-BED1CCB209DC}" name="Taken from" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{35962C17-3057-4CB9-8C5C-BED1CCB209DC}" name="Taken from" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -22736,11 +22741,11 @@
         <v>239</v>
       </c>
       <c r="E7" s="104">
-        <f>'4.7.1.1-2 Manure Methane'!E113</f>
+        <f>VEERG_4_7_1_1__1_TotalAnnualMethaneProductionFromManureManagementOtherLivestock_Result_Method1</f>
         <v>11.990348051537779</v>
       </c>
       <c r="F7" s="104">
-        <f>'4.7.1.1-2 Manure Methane'!O113</f>
+        <f>VEERG_4_7_1_1__1_TotalAnnualMethaneProductionFromManureManagementOtherLivestock_Result_Method2</f>
         <v>12.103057674611057</v>
       </c>
       <c r="G7" s="53" t="str">
@@ -22770,7 +22775,7 @@
         <v>240</v>
       </c>
       <c r="E8" s="104">
-        <f>'4.7.1.3-4 Soil Direct N2O'!E70</f>
+        <f>VEERG_4_7_1_3__1_DirectNitrousOxideEmissionsFromSoil_Result_Method1</f>
         <v>519.12802857142856</v>
       </c>
       <c r="F8" s="104">
@@ -22804,7 +22809,7 @@
         <v>241</v>
       </c>
       <c r="E9" s="104">
-        <f>'4.7.1.5-6 Soil Atmos Deposition'!E81</f>
+        <f>VEERG_4_7_1_5__1_AtmosphericDepositionEmissionsFromPasture_Result_Method1</f>
         <v>186.11705144999996</v>
       </c>
       <c r="F9" s="104">
@@ -22838,7 +22843,7 @@
         <v>238</v>
       </c>
       <c r="E10" s="104">
-        <f>'4.7.1.7-8 Soil Leaching Runoff'!E72</f>
+        <f>VEERG_4_7_1_7__1_LeachingAndRunoffEmissionsFromPasture_Result_Method1</f>
         <v>3.0587417142857145</v>
       </c>
       <c r="F10" s="104">
